--- a/Restaurent Menu.xlsx
+++ b/Restaurent Menu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5213538eb41c986f/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24C584C5-0887-4CA5-AF95-EFE03DBE99A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{24C584C5-0887-4CA5-AF95-EFE03DBE99A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9318B4D-DCC6-42CA-BB98-ACBC3417E6AA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D9F01F7-A9B8-413F-AC05-FAF5EFEB7844}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="35">
   <si>
     <t>Name of the Dish</t>
   </si>
@@ -115,6 +115,30 @@
   </si>
   <si>
     <t>South Indian Meals</t>
+  </si>
+  <si>
+    <t>Dish's Type</t>
+  </si>
+  <si>
+    <t>Lunch</t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t>Breakfast, Lunch, Dinner</t>
+  </si>
+  <si>
+    <t>Breakfast, Dinner</t>
+  </si>
+  <si>
+    <t>Idly</t>
+  </si>
+  <si>
+    <t>Sambar Idly</t>
+  </si>
+  <si>
+    <t>Chappathi</t>
   </si>
 </sst>
 </file>
@@ -158,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -166,6 +190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,10 +505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05174555-42F3-408C-8DD4-1F7EE38ED744}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -496,8 +524,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E1" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>19</v>
       </c>
@@ -510,8 +541,11 @@
       <c r="D2" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -524,8 +558,11 @@
       <c r="D3" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -538,8 +575,11 @@
       <c r="D4" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -552,8 +592,11 @@
       <c r="D5" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -566,8 +609,11 @@
       <c r="D6" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -580,8 +626,11 @@
       <c r="D7" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -594,8 +643,11 @@
       <c r="D8" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -608,8 +660,11 @@
       <c r="D9" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -622,8 +677,11 @@
       <c r="D10" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -636,8 +694,11 @@
       <c r="D11" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -650,8 +711,11 @@
       <c r="D12" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
@@ -664,8 +728,11 @@
       <c r="D13" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
@@ -678,8 +745,11 @@
       <c r="D14" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -692,8 +762,11 @@
       <c r="D15" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -706,8 +779,11 @@
       <c r="D16" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
@@ -720,8 +796,11 @@
       <c r="D17" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -734,8 +813,11 @@
       <c r="D18" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -748,8 +830,11 @@
       <c r="D19" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>17</v>
       </c>
@@ -762,8 +847,11 @@
       <c r="D20" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>16</v>
       </c>
@@ -775,6 +863,60 @@
       </c>
       <c r="D21" s="2">
         <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2">
+        <v>110</v>
+      </c>
+      <c r="D22" s="2">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2">
+        <v>50</v>
+      </c>
+      <c r="D23" s="2">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2">
+        <v>40</v>
+      </c>
+      <c r="D24" s="2">
+        <v>5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
